--- a/results/MASTER_RESULTS_SUMMARY.xlsx
+++ b/results/MASTER_RESULTS_SUMMARY.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:S9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,378 +448,571 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>ece</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>brier_score_mean</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>model_name</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>uq_mean_uncertainty</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>mean_unc_mean</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>mean_unc_max</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>mean_entropy</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>F1_KL0</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>F1_KL1</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>F1_KL2</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>F1_KL3</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>F1_KL4</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Brier_KL0</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Brier_KL1</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Brier_KL2</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Brier_KL3</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Brier_KL4</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.8226</v>
+        <v>0.8362000000000001</v>
       </c>
       <c r="B2" t="n">
-        <v>0.8098</v>
+        <v>0.8344</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9344</v>
-      </c>
-      <c r="D2" t="inlineStr">
+        <v>0.9334</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.1245</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.0519</v>
+      </c>
+      <c r="F2" t="inlineStr">
         <is>
           <t>resnet50_Homogeneous</t>
         </is>
       </c>
-      <c r="E2" t="n">
-        <v>0.05308337137103081</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.8452</v>
-      </c>
       <c r="G2" t="n">
-        <v>0.6393</v>
+        <v>0.057844</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7042</v>
+        <v>0.129542</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9062</v>
+        <v>0.782951</v>
       </c>
       <c r="J2" t="n">
-        <v>0.9538</v>
+        <v>0.8861</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.7465000000000001</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.6768999999999999</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.9394</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.9231</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.0528</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.109</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.064</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.0182</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.0157</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.8898</v>
+        <v>0.9233</v>
       </c>
       <c r="B3" t="n">
-        <v>0.8838</v>
+        <v>0.9271</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9455</v>
-      </c>
-      <c r="D3" t="inlineStr">
+        <v>0.9658</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.1302</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.0328</v>
+      </c>
+      <c r="F3" t="inlineStr">
         <is>
           <t>efficientnet_b3_Homogeneous</t>
         </is>
       </c>
-      <c r="E3" t="n">
-        <v>0.09248244017362595</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.8696</v>
-      </c>
       <c r="G3" t="n">
-        <v>0.7727000000000001</v>
+        <v>0.082691</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8529</v>
+        <v>0.184967</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9394</v>
+        <v>0.536021</v>
       </c>
       <c r="J3" t="n">
-        <v>0.9841</v>
+        <v>0.9308</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.8794</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.8571</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.9846</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.9836</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.0402</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.06809999999999999</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.0357</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.0091</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.011</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.9245</v>
+        <v>0.9438</v>
       </c>
       <c r="B4" t="n">
-        <v>0.9206</v>
+        <v>0.9515</v>
       </c>
       <c r="C4" t="n">
-        <v>0.9639</v>
-      </c>
-      <c r="D4" t="inlineStr">
+        <v>0.9809</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.1155</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.0222</v>
+      </c>
+      <c r="F4" t="inlineStr">
         <is>
           <t>densenet121_Homogeneous</t>
         </is>
       </c>
-      <c r="E4" t="n">
-        <v>0.04474717006087303</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.9091</v>
-      </c>
       <c r="G4" t="n">
-        <v>0.8429</v>
+        <v>0.048319</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8824</v>
+        <v>0.112588</v>
       </c>
       <c r="I4" t="n">
+        <v>0.516435</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.9367</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.8966</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.9394</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.9846</v>
+      </c>
+      <c r="N4" t="n">
         <v>1</v>
       </c>
-      <c r="J4" t="n">
-        <v>0.9688</v>
+      <c r="O4" t="n">
+        <v>0.0301</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.0516</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.0223</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.0037</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.0034</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.8973</v>
+        <v>0.9429</v>
       </c>
       <c r="B5" t="n">
-        <v>0.8877</v>
+        <v>0.9479</v>
       </c>
       <c r="C5" t="n">
-        <v>0.9478</v>
-      </c>
-      <c r="D5" t="inlineStr">
+        <v>0.9808</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.08939999999999999</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.0203</v>
+      </c>
+      <c r="F5" t="inlineStr">
         <is>
           <t>mobilenetv3_large_Homogeneous</t>
         </is>
       </c>
-      <c r="E5" t="n">
-        <v>0.06174319609999657</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.8957000000000001</v>
-      </c>
       <c r="G5" t="n">
-        <v>0.7717000000000001</v>
+        <v>0.055479</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8493000000000001</v>
+        <v>0.128705</v>
       </c>
       <c r="I5" t="n">
-        <v>0.9841</v>
+        <v>0.379889</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9375</v>
+        <v>0.9434</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.9014</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.9412</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.9697</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.9836</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.0279</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.0421</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.0179</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.0057</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0.9</v>
+        <v>0.9105</v>
       </c>
       <c r="B6" t="n">
-        <v>0.8892</v>
+        <v>0.9108000000000001</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9587</v>
-      </c>
-      <c r="D6" t="inlineStr">
+        <v>0.9725</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.08939999999999999</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.0294</v>
+      </c>
+      <c r="F6" t="inlineStr">
         <is>
           <t>convnext_tiny_Homogeneous</t>
         </is>
       </c>
-      <c r="E6" t="n">
-        <v>0.05844758823513985</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.929</v>
-      </c>
       <c r="G6" t="n">
-        <v>0.8270999999999999</v>
+        <v>0.052503</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7838000000000001</v>
+        <v>0.123055</v>
       </c>
       <c r="I6" t="n">
-        <v>0.9375</v>
+        <v>0.447133</v>
       </c>
       <c r="J6" t="n">
-        <v>0.9688</v>
+        <v>0.9068000000000001</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.8175</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.8451</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.9846</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.0419</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.0659</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.0287</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.0048</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.0054</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0.9206</v>
+        <v>0.9428</v>
       </c>
       <c r="B7" t="n">
-        <v>0.9136</v>
+        <v>0.9505</v>
       </c>
       <c r="C7" t="n">
-        <v>0.9665</v>
-      </c>
-      <c r="D7" t="inlineStr">
+        <v>0.9819</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.1359</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.0242</v>
+      </c>
+      <c r="F7" t="inlineStr">
         <is>
           <t>Heterogeneous_Avg</t>
         </is>
       </c>
-      <c r="E7" t="n">
-        <v>0.0744754821062088</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0.9202</v>
-      </c>
       <c r="G7" t="n">
-        <v>0.8217</v>
+        <v>0.06685000000000001</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8571</v>
+        <v>0.153702</v>
       </c>
       <c r="I7" t="n">
-        <v>0.9846</v>
+        <v>0.507584</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9841</v>
+        <v>0.9494</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.9103</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.9394</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.9697</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.9836</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.0314</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.0524</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.0235</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.0068</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.0068</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0.9206</v>
+        <v>0.9428</v>
       </c>
       <c r="B8" t="n">
-        <v>0.9136</v>
+        <v>0.9505</v>
       </c>
       <c r="C8" t="n">
-        <v>0.9665</v>
-      </c>
-      <c r="D8" t="inlineStr">
+        <v>0.9819</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.1335</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.0238</v>
+      </c>
+      <c r="F8" t="inlineStr">
         <is>
           <t>Heterogeneous_Weighted</t>
         </is>
       </c>
-      <c r="E8" t="n">
-        <v>0.0744754821062088</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0.9202</v>
-      </c>
       <c r="G8" t="n">
-        <v>0.8217</v>
+        <v>0.06685000000000001</v>
       </c>
       <c r="H8" t="n">
-        <v>0.8571</v>
+        <v>0.153702</v>
       </c>
       <c r="I8" t="n">
-        <v>0.9846</v>
+        <v>0.500561</v>
       </c>
       <c r="J8" t="n">
-        <v>0.9841</v>
+        <v>0.9494</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.9103</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.9394</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.9697</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.9836</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.0311</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.0522</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.0224</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.0064</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.0068</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0.9268999999999999</v>
+        <v>0.9550999999999999</v>
       </c>
       <c r="B9" t="n">
-        <v>0.9201</v>
+        <v>0.9585</v>
       </c>
       <c r="C9" t="n">
-        <v>0.9644</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Mega_Ensemble_TypD</t>
-        </is>
+        <v>0.983</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.1584</v>
       </c>
       <c r="E9" t="n">
-        <v>0.09592271596193314</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.9125</v>
+        <v>0.0262</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Mega_Ensemble</t>
+        </is>
       </c>
       <c r="G9" t="n">
-        <v>0.8333</v>
+        <v>0.088363</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8857</v>
+        <v>0.187498</v>
       </c>
       <c r="I9" t="n">
+        <v>0.599092</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.9434</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.9078000000000001</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.9565</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.9846</v>
+      </c>
+      <c r="N9" t="n">
         <v>1</v>
       </c>
-      <c r="J9" t="n">
-        <v>0.9688</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>0.9005</v>
-      </c>
-      <c r="B10" t="n">
-        <v>0.8962</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0.9592000000000001</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Class_Specific_With_Rep</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>0.04468469694256783</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0.8974</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0.8260999999999999</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0.8657</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0.9524</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0.9394</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>0.9001</v>
-      </c>
-      <c r="B11" t="n">
-        <v>0.8965</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0.962</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Class_Specific_Unique</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>0.05364396050572395</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0.8974</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0.8260999999999999</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0.8696</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0.9355</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0.9538</v>
+      <c r="O9" t="n">
+        <v>0.033</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.0588</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.0272</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.0063</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.0059</v>
       </c>
     </row>
   </sheetData>
@@ -833,7 +1026,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:AL9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -844,62 +1037,187 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>threshold</t>
+          <t>n_total</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>auroc_uncertain_detection</t>
+          <t>n_expert_uncertain</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>f1_uncertain</t>
+          <t>threshold_source</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>n_total</t>
+          <t>threshold_unc_mean</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>n_expert_uncertain</t>
+          <t>threshold_unc_max</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>n_ensemble_flagged</t>
+          <t>threshold_entropy</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>mean_unc_certain</t>
+          <t>auroc_unc_mean</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>mean_unc_uncertain</t>
+          <t>auprc_unc_mean</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>TN (Certain_ok)</t>
+          <t>f1_uncertain_unc_mean</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>FP (False_Uncertain)</t>
+          <t>n_flagged_unc_mean</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>FN (Missed_Uncertain)</t>
+          <t>mean_unc_certain_unc_mean</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>TP (True_Uncertain)</t>
+          <t>mean_unc_uncertain_unc_mean</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>auroc_unc_max</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>auprc_unc_max</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>f1_uncertain_unc_max</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>n_flagged_unc_max</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>mean_unc_certain_unc_max</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>mean_unc_uncertain_unc_max</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>auroc_entropy</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>auprc_entropy</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>f1_uncertain_entropy</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>n_flagged_entropy</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>mean_unc_certain_entropy</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>mean_unc_uncertain_entropy</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>best_signal_by_auroc</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>TN_unc_mean</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>FP_unc_mean</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>FN_unc_mean</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>TP_unc_mean</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>TN_unc_max</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>FP_unc_max</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>FN_unc_max</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>TP_unc_max</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>TN_entropy</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>FP_entropy</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>FN_entropy</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>TP_entropy</t>
         </is>
       </c>
     </row>
@@ -910,40 +1228,119 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.147687</v>
+        <v>1650</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6025</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0</v>
+        <v>11</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Mega Ensemble on CV set, 95th percentile per signal</t>
+        </is>
       </c>
       <c r="E2" t="n">
-        <v>245</v>
+        <v>0.164941</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>0.323527</v>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>1.10247</v>
       </c>
       <c r="H2" t="n">
-        <v>0.053057</v>
+        <v>0.61</v>
       </c>
       <c r="I2" t="n">
-        <v>0.059521</v>
+        <v>0.0114</v>
       </c>
       <c r="J2" t="n">
-        <v>243</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
         <v>1</v>
       </c>
       <c r="L2" t="n">
+        <v>0.057758</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.070671</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.6198</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.0112</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>15</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.129344</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.159104</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.6744</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0.0156</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.0351</v>
+      </c>
+      <c r="W2" t="n">
+        <v>274</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0.781684</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.971714</v>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>entropy</t>
+        </is>
+      </c>
+      <c r="AA2" t="n">
+        <v>1638</v>
+      </c>
+      <c r="AB2" t="n">
         <v>1</v>
       </c>
-      <c r="M2" t="n">
-        <v>0</v>
+      <c r="AC2" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1624</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>1370</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>269</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -953,39 +1350,118 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.28025</v>
+        <v>1650</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6475</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0</v>
+        <v>11</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Mega Ensemble on CV set, 95th percentile per signal</t>
+        </is>
       </c>
       <c r="E3" t="n">
-        <v>245</v>
+        <v>0.164941</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>0.323527</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>1.10247</v>
       </c>
       <c r="H3" t="n">
-        <v>0.092325</v>
+        <v>0.6026</v>
       </c>
       <c r="I3" t="n">
-        <v>0.130776</v>
+        <v>0.0128</v>
       </c>
       <c r="J3" t="n">
-        <v>244</v>
+        <v>0.0375</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>149</v>
       </c>
       <c r="L3" t="n">
-        <v>1</v>
+        <v>0.08255800000000001</v>
       </c>
       <c r="M3" t="n">
+        <v>0.102624</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.6172</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.0259</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.0286</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>339</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.184632</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.234968</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0.5936</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0.009599999999999999</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>97</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0.535322</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0.640161</v>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>unc_max</t>
+        </is>
+      </c>
+      <c r="AA3" t="n">
+        <v>1493</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>146</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1305</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>334</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>1542</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>97</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>11</v>
+      </c>
+      <c r="AL3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -996,40 +1472,119 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.168946</v>
+        <v>1650</v>
       </c>
       <c r="C4" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
+        <v>11</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Mega Ensemble on CV set, 95th percentile per signal</t>
+        </is>
       </c>
       <c r="E4" t="n">
-        <v>245</v>
+        <v>0.164941</v>
       </c>
       <c r="F4" t="n">
+        <v>0.323527</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.10247</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.5626</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>8</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.048301</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.050969</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.5626</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.0083</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>39</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.112524</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.122197</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.6607</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.0134</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.0256</v>
+      </c>
+      <c r="W4" t="n">
+        <v>67</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.515342</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.679283</v>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>entropy</t>
+        </is>
+      </c>
+      <c r="AA4" t="n">
+        <v>1631</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1600</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>39</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>1573</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>66</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>10</v>
+      </c>
+      <c r="AL4" t="n">
         <v>1</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.044634</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0.07245799999999999</v>
-      </c>
-      <c r="J4" t="n">
-        <v>244</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>1</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -1039,39 +1594,118 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.228748</v>
+        <v>1650</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8074</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0</v>
+        <v>11</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Mega Ensemble on CV set, 95th percentile per signal</t>
+        </is>
       </c>
       <c r="E5" t="n">
-        <v>245</v>
+        <v>0.164941</v>
       </c>
       <c r="F5" t="n">
+        <v>0.323527</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.10247</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.7597</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.0193</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.0364</v>
+      </c>
+      <c r="K5" t="n">
+        <v>44</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.055151</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.104374</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.7377</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.0185</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.0222</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>169</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.128037</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.228251</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.7722</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.0183</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>26</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0.377907</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0.675157</v>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>entropy</t>
+        </is>
+      </c>
+      <c r="AA5" t="n">
+        <v>1596</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>43</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD5" t="n">
         <v>1</v>
       </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.061508</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0.11919</v>
-      </c>
-      <c r="J5" t="n">
-        <v>244</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1</v>
-      </c>
-      <c r="M5" t="n">
+      <c r="AE5" t="n">
+        <v>1472</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>167</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>9</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>1613</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>26</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>11</v>
+      </c>
+      <c r="AL5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1082,39 +1716,118 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.175857</v>
+        <v>1650</v>
       </c>
       <c r="C6" t="n">
-        <v>0.6967</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0</v>
+        <v>11</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Mega Ensemble on CV set, 95th percentile per signal</t>
+        </is>
       </c>
       <c r="E6" t="n">
-        <v>245</v>
+        <v>0.164941</v>
       </c>
       <c r="F6" t="n">
+        <v>0.323527</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.10247</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.5693</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.0108</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>22</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.052445</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.061133</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.5763</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.0101</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.0208</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>85</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.12291</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.144792</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.6448</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.0138</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>25</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.446172</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.590358</v>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>entropy</t>
+        </is>
+      </c>
+      <c r="AA6" t="n">
+        <v>1617</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>22</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1555</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>84</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH6" t="n">
         <v>1</v>
       </c>
-      <c r="G6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.058368</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0.07788200000000001</v>
-      </c>
-      <c r="J6" t="n">
-        <v>243</v>
-      </c>
-      <c r="K6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1</v>
-      </c>
-      <c r="M6" t="n">
+      <c r="AI6" t="n">
+        <v>1614</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>25</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>11</v>
+      </c>
+      <c r="AL6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1125,39 +1838,118 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.224507</v>
+        <v>1650</v>
       </c>
       <c r="C7" t="n">
-        <v>0.9139</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0</v>
+        <v>11</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Mega Ensemble on CV set, 95th percentile per signal</t>
+        </is>
       </c>
       <c r="E7" t="n">
-        <v>245</v>
+        <v>0.164941</v>
       </c>
       <c r="F7" t="n">
+        <v>0.323527</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.10247</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.5094</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.0072</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>43</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.066873</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.063397</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.5144</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.0074</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.0131</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>142</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.153734</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.149033</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.6157</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0.0108</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>36</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0.5068859999999999</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0.611511</v>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>entropy</t>
+        </is>
+      </c>
+      <c r="AA7" t="n">
+        <v>1596</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>43</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1498</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>141</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH7" t="n">
         <v>1</v>
       </c>
-      <c r="G7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0.07416200000000001</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0.151033</v>
-      </c>
-      <c r="J7" t="n">
-        <v>244</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1</v>
-      </c>
-      <c r="M7" t="n">
+      <c r="AI7" t="n">
+        <v>1603</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>36</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>11</v>
+      </c>
+      <c r="AL7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1168,169 +1960,241 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.224507</v>
+        <v>1650</v>
       </c>
       <c r="C8" t="n">
-        <v>0.9139</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0</v>
+        <v>11</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Mega Ensemble on CV set, 95th percentile per signal</t>
+        </is>
       </c>
       <c r="E8" t="n">
-        <v>245</v>
+        <v>0.164941</v>
       </c>
       <c r="F8" t="n">
+        <v>0.323527</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.10247</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.5094</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.0072</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>43</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.066873</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.063397</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.5144</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.0074</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.0131</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>142</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.153734</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.149033</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.6148</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0.0107</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>35</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0.499875</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0.602816</v>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>entropy</t>
+        </is>
+      </c>
+      <c r="AA8" t="n">
+        <v>1596</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>43</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1498</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>141</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH8" t="n">
         <v>1</v>
       </c>
-      <c r="G8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0.07416200000000001</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0.151033</v>
-      </c>
-      <c r="J8" t="n">
-        <v>244</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1</v>
-      </c>
-      <c r="M8" t="n">
+      <c r="AI8" t="n">
+        <v>1604</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>35</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>11</v>
+      </c>
+      <c r="AL8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Mega_Ensemble_TypD</t>
+          <t>Mega_Ensemble</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.23774</v>
+        <v>1650</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7295</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
+        <v>11</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Mega Ensemble on CV set, 95th percentile per signal</t>
+        </is>
       </c>
       <c r="E9" t="n">
-        <v>245</v>
+        <v>0.164941</v>
       </c>
       <c r="F9" t="n">
+        <v>0.323527</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.10247</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.6614</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.0119</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>79</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.0882</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.112617</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.6767</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.0144</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>77</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.187142</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.240556</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.6921</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0.0133</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0.0208</v>
+      </c>
+      <c r="W9" t="n">
+        <v>85</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0.597809</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0.790261</v>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>entropy</t>
+        </is>
+      </c>
+      <c r="AA9" t="n">
+        <v>1560</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>79</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1562</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>77</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>1555</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>84</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>10</v>
+      </c>
+      <c r="AL9" t="n">
         <v>1</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.095792</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.127825</v>
-      </c>
-      <c r="J9" t="n">
-        <v>244</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Class_Specific_With_Rep</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>0.18306</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0.6926</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="n">
-        <v>245</v>
-      </c>
-      <c r="F10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0.044635</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0.056701</v>
-      </c>
-      <c r="J10" t="n">
-        <v>244</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Class_Specific_Unique</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>0.207956</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0.8115</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="n">
-        <v>245</v>
-      </c>
-      <c r="F11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" t="n">
-        <v>1</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0.05341</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0.11085</v>
-      </c>
-      <c r="J11" t="n">
-        <v>243</v>
-      </c>
-      <c r="K11" t="n">
-        <v>1</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1344,7 +2208,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1393,6 +2257,11 @@
           <t>ensemble_name</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>unc_signal</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1401,31 +2270,36 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>66</v>
+        <v>5551.5</v>
       </c>
       <c r="C2" t="n">
-        <v>0.216305</v>
+        <v>0.013958</v>
       </c>
       <c r="D2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>0.459</v>
+        <v>0.3842</v>
       </c>
       <c r="F2" t="n">
-        <v>244</v>
+        <v>1639</v>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>p=0.2163 &gt;= 0.05 statistically insignificant difference, r=0.459 (average efect)</t>
+          <t>p=0.0140 &lt; 0.05 — statistically significant difference, r=0.384 (medium effect)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Mega_Ensemble_TypD</t>
+          <t>Mega_Ensemble</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>entropy</t>
         </is>
       </c>
     </row>
